--- a/src/test/resources/DataCRM/DataCRM.xlsx
+++ b/src/test/resources/DataCRM/DataCRM.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="10470" windowHeight="5205"/>
+    <workbookView windowWidth="10470" windowHeight="4485"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>EMAIL</t>
   </si>
@@ -40,10 +40,19 @@
     <t>admin@example.com</t>
   </si>
   <si>
+    <t>123456</t>
+  </si>
+  <si>
     <t>ngadmin@gmail.com</t>
   </si>
   <si>
     <t>ng123567</t>
+  </si>
+  <si>
+    <t>admin23@gmail.com</t>
+  </si>
+  <si>
+    <t>6786838</t>
   </si>
 </sst>
 </file>
@@ -655,12 +664,19 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="6"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" quotePrefix="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1000,11 +1016,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3" outlineLevelCol="1"/>
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="3" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="23.425" customWidth="1"/>
     <col min="2" max="2" width="16.5" customWidth="1"/>
+    <col min="3" max="3" width="11.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1015,29 +1032,36 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:3">
       <c r="A2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1">
-        <v>123456</v>
+      <c r="B2" s="4" t="s">
+        <v>3</v>
       </c>
+      <c r="C2" s="3"/>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" s="2"/>
+    <row r="4" spans="1:2">
+      <c r="A4" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>7</v>
+      </c>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="admin@example.com"/>
     <hyperlink ref="A3" r:id="rId2" display="ngadmin@gmail.com"/>
+    <hyperlink ref="A4" r:id="rId3" display="admin23@gmail.com"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
